--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119916886</v>
+        <v>119917267</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>96862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1272,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593523</v>
+        <v>593527</v>
       </c>
       <c r="R7" t="n">
-        <v>6987471</v>
+        <v>6987563</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119916586</v>
+        <v>119916886</v>
       </c>
       <c r="B8" t="n">
-        <v>90067</v>
+        <v>90562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>256703</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593618</v>
+        <v>593523</v>
       </c>
       <c r="R8" t="n">
-        <v>6987530</v>
+        <v>6987471</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119917111</v>
+        <v>119916779</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>77910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593461</v>
+        <v>593554</v>
       </c>
       <c r="R9" t="n">
-        <v>6987454</v>
+        <v>6987490</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119916468</v>
+        <v>119917383</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>90905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593608</v>
+        <v>593481</v>
       </c>
       <c r="R10" t="n">
-        <v>6987529</v>
+        <v>6987561</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119917267</v>
+        <v>119917111</v>
       </c>
       <c r="B13" t="n">
-        <v>96862</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593527</v>
+        <v>593461</v>
       </c>
       <c r="R13" t="n">
-        <v>6987563</v>
+        <v>6987454</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119916779</v>
+        <v>119916586</v>
       </c>
       <c r="B14" t="n">
-        <v>77910</v>
+        <v>90067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1986,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>256703</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593554</v>
+        <v>593618</v>
       </c>
       <c r="R14" t="n">
-        <v>6987490</v>
+        <v>6987530</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119917383</v>
+        <v>119916468</v>
       </c>
       <c r="B15" t="n">
-        <v>90905</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,25 +2088,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593481</v>
+        <v>593608</v>
       </c>
       <c r="R15" t="n">
-        <v>6987561</v>
+        <v>6987529</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119917267</v>
+        <v>119916468</v>
       </c>
       <c r="B7" t="n">
-        <v>96862</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593527</v>
+        <v>593608</v>
       </c>
       <c r="R7" t="n">
-        <v>6987563</v>
+        <v>6987529</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119916886</v>
+        <v>119917383</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593523</v>
+        <v>593481</v>
       </c>
       <c r="R8" t="n">
-        <v>6987471</v>
+        <v>6987561</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119916779</v>
+        <v>119917551</v>
       </c>
       <c r="B9" t="n">
-        <v>77910</v>
+        <v>91005</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593554</v>
+        <v>593594</v>
       </c>
       <c r="R9" t="n">
-        <v>6987490</v>
+        <v>6987625</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119917383</v>
+        <v>119917111</v>
       </c>
       <c r="B10" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593481</v>
+        <v>593461</v>
       </c>
       <c r="R10" t="n">
-        <v>6987561</v>
+        <v>6987454</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119917551</v>
+        <v>119917267</v>
       </c>
       <c r="B11" t="n">
-        <v>91005</v>
+        <v>96862</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593594</v>
+        <v>593527</v>
       </c>
       <c r="R11" t="n">
-        <v>6987625</v>
+        <v>6987563</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119917111</v>
+        <v>119916886</v>
       </c>
       <c r="B13" t="n">
         <v>90562</v>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593461</v>
+        <v>593523</v>
       </c>
       <c r="R13" t="n">
-        <v>6987454</v>
+        <v>6987471</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119916586</v>
+        <v>119916779</v>
       </c>
       <c r="B14" t="n">
-        <v>90067</v>
+        <v>77910</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1986,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>256703</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593618</v>
+        <v>593554</v>
       </c>
       <c r="R14" t="n">
-        <v>6987530</v>
+        <v>6987490</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119916468</v>
+        <v>119916586</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>90067</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,21 +2092,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593608</v>
+        <v>593618</v>
       </c>
       <c r="R15" t="n">
-        <v>6987529</v>
+        <v>6987530</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119916468</v>
+        <v>119916886</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1272,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593608</v>
+        <v>593523</v>
       </c>
       <c r="R7" t="n">
-        <v>6987529</v>
+        <v>6987471</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119917383</v>
+        <v>119916779</v>
       </c>
       <c r="B8" t="n">
-        <v>90905</v>
+        <v>77910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593481</v>
+        <v>593554</v>
       </c>
       <c r="R8" t="n">
-        <v>6987561</v>
+        <v>6987490</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119917551</v>
+        <v>119916586</v>
       </c>
       <c r="B9" t="n">
-        <v>91005</v>
+        <v>90067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>256703</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593594</v>
+        <v>593618</v>
       </c>
       <c r="R9" t="n">
-        <v>6987625</v>
+        <v>6987530</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119917111</v>
+        <v>119917267</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>96862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593461</v>
+        <v>593527</v>
       </c>
       <c r="R10" t="n">
-        <v>6987454</v>
+        <v>6987563</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119917267</v>
+        <v>119917111</v>
       </c>
       <c r="B11" t="n">
-        <v>96862</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593527</v>
+        <v>593461</v>
       </c>
       <c r="R11" t="n">
-        <v>6987563</v>
+        <v>6987454</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119917390</v>
+        <v>119916468</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593481</v>
+        <v>593608</v>
       </c>
       <c r="R12" t="n">
-        <v>6987562</v>
+        <v>6987529</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119916886</v>
+        <v>119917551</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>91005</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593523</v>
+        <v>593594</v>
       </c>
       <c r="R13" t="n">
-        <v>6987471</v>
+        <v>6987625</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119916779</v>
+        <v>119917383</v>
       </c>
       <c r="B14" t="n">
-        <v>77910</v>
+        <v>90905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1986,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593554</v>
+        <v>593481</v>
       </c>
       <c r="R14" t="n">
-        <v>6987490</v>
+        <v>6987561</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119916586</v>
+        <v>119917390</v>
       </c>
       <c r="B15" t="n">
-        <v>90067</v>
+        <v>90562</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,25 +2088,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>256703</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593618</v>
+        <v>593481</v>
       </c>
       <c r="R15" t="n">
-        <v>6987530</v>
+        <v>6987562</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119916468</v>
+        <v>119917551</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593608</v>
+        <v>593594</v>
       </c>
       <c r="R12" t="n">
-        <v>6987529</v>
+        <v>6987625</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119917551</v>
+        <v>119916468</v>
       </c>
       <c r="B13" t="n">
-        <v>91005</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593594</v>
+        <v>593608</v>
       </c>
       <c r="R13" t="n">
-        <v>6987625</v>
+        <v>6987529</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119917551</v>
+        <v>119916468</v>
       </c>
       <c r="B12" t="n">
-        <v>91005</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593594</v>
+        <v>593608</v>
       </c>
       <c r="R12" t="n">
-        <v>6987625</v>
+        <v>6987529</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119916468</v>
+        <v>119917551</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91005</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593608</v>
+        <v>593594</v>
       </c>
       <c r="R13" t="n">
-        <v>6987529</v>
+        <v>6987625</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119916886</v>
+        <v>119917111</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593523</v>
+        <v>593461</v>
       </c>
       <c r="R7" t="n">
-        <v>6987471</v>
+        <v>6987454</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119916779</v>
+        <v>119916586</v>
       </c>
       <c r="B8" t="n">
-        <v>77910</v>
+        <v>90084</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>256703</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593554</v>
+        <v>593618</v>
       </c>
       <c r="R8" t="n">
-        <v>6987490</v>
+        <v>6987530</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119916586</v>
+        <v>119917551</v>
       </c>
       <c r="B9" t="n">
-        <v>90067</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>256703</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593618</v>
+        <v>593594</v>
       </c>
       <c r="R9" t="n">
-        <v>6987530</v>
+        <v>6987625</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119917267</v>
+        <v>119917383</v>
       </c>
       <c r="B10" t="n">
-        <v>96862</v>
+        <v>90923</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593527</v>
+        <v>593481</v>
       </c>
       <c r="R10" t="n">
-        <v>6987563</v>
+        <v>6987561</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119917111</v>
+        <v>119916886</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593461</v>
+        <v>593523</v>
       </c>
       <c r="R11" t="n">
-        <v>6987454</v>
+        <v>6987471</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119916468</v>
+        <v>119916779</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>77926</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593608</v>
+        <v>593554</v>
       </c>
       <c r="R12" t="n">
-        <v>6987529</v>
+        <v>6987490</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119917551</v>
+        <v>119916468</v>
       </c>
       <c r="B13" t="n">
-        <v>91005</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593594</v>
+        <v>593608</v>
       </c>
       <c r="R13" t="n">
-        <v>6987625</v>
+        <v>6987529</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119917383</v>
+        <v>119917390</v>
       </c>
       <c r="B14" t="n">
-        <v>90905</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1986,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,7 +2017,7 @@
         <v>593481</v>
       </c>
       <c r="R14" t="n">
-        <v>6987561</v>
+        <v>6987562</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119917390</v>
+        <v>119917267</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>96885</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,25 +2088,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593481</v>
+        <v>593527</v>
       </c>
       <c r="R15" t="n">
-        <v>6987562</v>
+        <v>6987563</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119917111</v>
+        <v>119917267</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1272,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593461</v>
+        <v>593527</v>
       </c>
       <c r="R7" t="n">
-        <v>6987454</v>
+        <v>6987563</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119916586</v>
+        <v>119917111</v>
       </c>
       <c r="B8" t="n">
-        <v>90084</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>256703</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593618</v>
+        <v>593461</v>
       </c>
       <c r="R8" t="n">
-        <v>6987530</v>
+        <v>6987454</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119917551</v>
+        <v>119916468</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593594</v>
+        <v>593608</v>
       </c>
       <c r="R9" t="n">
-        <v>6987625</v>
+        <v>6987529</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119916886</v>
+        <v>119916779</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>77926</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593523</v>
+        <v>593554</v>
       </c>
       <c r="R11" t="n">
-        <v>6987471</v>
+        <v>6987490</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119916779</v>
+        <v>119917390</v>
       </c>
       <c r="B12" t="n">
-        <v>77926</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,21 +1786,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593554</v>
+        <v>593481</v>
       </c>
       <c r="R12" t="n">
-        <v>6987490</v>
+        <v>6987562</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119916468</v>
+        <v>119916586</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>90084</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593608</v>
+        <v>593618</v>
       </c>
       <c r="R13" t="n">
-        <v>6987529</v>
+        <v>6987530</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119917390</v>
+        <v>119917551</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1986,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593481</v>
+        <v>593594</v>
       </c>
       <c r="R14" t="n">
-        <v>6987562</v>
+        <v>6987625</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119917267</v>
+        <v>119916886</v>
       </c>
       <c r="B15" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,25 +2088,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593527</v>
+        <v>593523</v>
       </c>
       <c r="R15" t="n">
-        <v>6987563</v>
+        <v>6987471</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119916586</v>
+        <v>119917551</v>
       </c>
       <c r="B13" t="n">
-        <v>90084</v>
+        <v>91023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>256703</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593618</v>
+        <v>593594</v>
       </c>
       <c r="R13" t="n">
-        <v>6987530</v>
+        <v>6987625</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119917551</v>
+        <v>119916886</v>
       </c>
       <c r="B14" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1986,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593594</v>
+        <v>593523</v>
       </c>
       <c r="R14" t="n">
-        <v>6987625</v>
+        <v>6987471</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119916886</v>
+        <v>119916586</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>90084</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,25 +2088,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>256703</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593523</v>
+        <v>593618</v>
       </c>
       <c r="R15" t="n">
-        <v>6987471</v>
+        <v>6987530</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119917267</v>
+        <v>119916586</v>
       </c>
       <c r="B7" t="n">
-        <v>96885</v>
+        <v>90084</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>256703</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593527</v>
+        <v>593618</v>
       </c>
       <c r="R7" t="n">
-        <v>6987563</v>
+        <v>6987530</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119917111</v>
+        <v>119916468</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593461</v>
+        <v>593608</v>
       </c>
       <c r="R8" t="n">
-        <v>6987454</v>
+        <v>6987529</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119916468</v>
+        <v>119917383</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>90923</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593608</v>
+        <v>593481</v>
       </c>
       <c r="R9" t="n">
-        <v>6987529</v>
+        <v>6987561</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119917383</v>
+        <v>119916886</v>
       </c>
       <c r="B10" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593481</v>
+        <v>593523</v>
       </c>
       <c r="R10" t="n">
-        <v>6987561</v>
+        <v>6987471</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119916779</v>
+        <v>119917111</v>
       </c>
       <c r="B11" t="n">
-        <v>77926</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593554</v>
+        <v>593461</v>
       </c>
       <c r="R11" t="n">
-        <v>6987490</v>
+        <v>6987454</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119917390</v>
+        <v>119917267</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593481</v>
+        <v>593527</v>
       </c>
       <c r="R12" t="n">
-        <v>6987562</v>
+        <v>6987563</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119917551</v>
+        <v>119916779</v>
       </c>
       <c r="B13" t="n">
-        <v>91023</v>
+        <v>77926</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593594</v>
+        <v>593554</v>
       </c>
       <c r="R13" t="n">
-        <v>6987625</v>
+        <v>6987490</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119916886</v>
+        <v>119917390</v>
       </c>
       <c r="B14" t="n">
         <v>90580</v>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593523</v>
+        <v>593481</v>
       </c>
       <c r="R14" t="n">
-        <v>6987471</v>
+        <v>6987562</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119916586</v>
+        <v>119917551</v>
       </c>
       <c r="B15" t="n">
-        <v>90084</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,25 +2088,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>256703</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593618</v>
+        <v>593594</v>
       </c>
       <c r="R15" t="n">
-        <v>6987530</v>
+        <v>6987625</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119917267</v>
+        <v>119916779</v>
       </c>
       <c r="B12" t="n">
-        <v>96885</v>
+        <v>77926</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593527</v>
+        <v>593554</v>
       </c>
       <c r="R12" t="n">
-        <v>6987563</v>
+        <v>6987490</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119916779</v>
+        <v>119917267</v>
       </c>
       <c r="B13" t="n">
-        <v>77926</v>
+        <v>96885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593554</v>
+        <v>593527</v>
       </c>
       <c r="R13" t="n">
-        <v>6987490</v>
+        <v>6987563</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119916586</v>
+        <v>119917111</v>
       </c>
       <c r="B7" t="n">
-        <v>90084</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1272,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>256703</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593618</v>
+        <v>593461</v>
       </c>
       <c r="R7" t="n">
-        <v>6987530</v>
+        <v>6987454</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119916468</v>
+        <v>119916886</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593608</v>
+        <v>593523</v>
       </c>
       <c r="R8" t="n">
-        <v>6987529</v>
+        <v>6987471</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119916886</v>
+        <v>119916779</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>77926</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593523</v>
+        <v>593554</v>
       </c>
       <c r="R10" t="n">
-        <v>6987471</v>
+        <v>6987490</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119917111</v>
+        <v>119917551</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593461</v>
+        <v>593594</v>
       </c>
       <c r="R11" t="n">
-        <v>6987454</v>
+        <v>6987625</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119916779</v>
+        <v>119917390</v>
       </c>
       <c r="B12" t="n">
-        <v>77926</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,21 +1786,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593554</v>
+        <v>593481</v>
       </c>
       <c r="R12" t="n">
-        <v>6987490</v>
+        <v>6987562</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119917267</v>
+        <v>119916586</v>
       </c>
       <c r="B13" t="n">
-        <v>96885</v>
+        <v>90084</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>256703</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593527</v>
+        <v>593618</v>
       </c>
       <c r="R13" t="n">
-        <v>6987563</v>
+        <v>6987530</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119917390</v>
+        <v>119917267</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1986,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593481</v>
+        <v>593527</v>
       </c>
       <c r="R14" t="n">
-        <v>6987562</v>
+        <v>6987563</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119917551</v>
+        <v>119916468</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,25 +2088,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593594</v>
+        <v>593608</v>
       </c>
       <c r="R15" t="n">
-        <v>6987625</v>
+        <v>6987529</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119917111</v>
+        <v>119917383</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1272,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593461</v>
+        <v>593481</v>
       </c>
       <c r="R7" t="n">
-        <v>6987454</v>
+        <v>6987561</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119916886</v>
+        <v>119917390</v>
       </c>
       <c r="B8" t="n">
         <v>90580</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593523</v>
+        <v>593481</v>
       </c>
       <c r="R8" t="n">
-        <v>6987471</v>
+        <v>6987562</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119917383</v>
+        <v>119917111</v>
       </c>
       <c r="B9" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593481</v>
+        <v>593461</v>
       </c>
       <c r="R9" t="n">
-        <v>6987561</v>
+        <v>6987454</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119916779</v>
+        <v>119916886</v>
       </c>
       <c r="B10" t="n">
-        <v>77926</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593554</v>
+        <v>593523</v>
       </c>
       <c r="R10" t="n">
-        <v>6987490</v>
+        <v>6987471</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119917551</v>
+        <v>119916779</v>
       </c>
       <c r="B11" t="n">
-        <v>91023</v>
+        <v>77926</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593594</v>
+        <v>593554</v>
       </c>
       <c r="R11" t="n">
-        <v>6987625</v>
+        <v>6987490</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119917390</v>
+        <v>119917267</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593481</v>
+        <v>593527</v>
       </c>
       <c r="R12" t="n">
-        <v>6987562</v>
+        <v>6987563</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119916586</v>
+        <v>119916468</v>
       </c>
       <c r="B13" t="n">
-        <v>90084</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593618</v>
+        <v>593608</v>
       </c>
       <c r="R13" t="n">
-        <v>6987530</v>
+        <v>6987529</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119917267</v>
+        <v>119916586</v>
       </c>
       <c r="B14" t="n">
-        <v>96885</v>
+        <v>90084</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>256703</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593527</v>
+        <v>593618</v>
       </c>
       <c r="R14" t="n">
-        <v>6987563</v>
+        <v>6987530</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119916468</v>
+        <v>119917551</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,25 +2088,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593608</v>
+        <v>593594</v>
       </c>
       <c r="R15" t="n">
-        <v>6987529</v>
+        <v>6987625</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119916886</v>
+        <v>119916779</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>77926</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593523</v>
+        <v>593554</v>
       </c>
       <c r="R10" t="n">
-        <v>6987471</v>
+        <v>6987490</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119916779</v>
+        <v>119917267</v>
       </c>
       <c r="B11" t="n">
-        <v>77926</v>
+        <v>96885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593554</v>
+        <v>593527</v>
       </c>
       <c r="R11" t="n">
-        <v>6987490</v>
+        <v>6987563</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119917267</v>
+        <v>119916886</v>
       </c>
       <c r="B12" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593527</v>
+        <v>593523</v>
       </c>
       <c r="R12" t="n">
-        <v>6987563</v>
+        <v>6987471</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 25649-2022 artfynd.xlsx
+++ b/artfynd/A 25649-2022 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119917383</v>
+        <v>119917551</v>
       </c>
       <c r="B7" t="n">
-        <v>90923</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593481</v>
+        <v>593594</v>
       </c>
       <c r="R7" t="n">
-        <v>6987561</v>
+        <v>6987625</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119917111</v>
+        <v>119916468</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593461</v>
+        <v>593608</v>
       </c>
       <c r="R9" t="n">
-        <v>6987454</v>
+        <v>6987529</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119916779</v>
+        <v>119916586</v>
       </c>
       <c r="B10" t="n">
-        <v>77926</v>
+        <v>90084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>256703</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593554</v>
+        <v>593618</v>
       </c>
       <c r="R10" t="n">
-        <v>6987490</v>
+        <v>6987530</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119917267</v>
+        <v>119917383</v>
       </c>
       <c r="B11" t="n">
-        <v>96885</v>
+        <v>90923</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>2062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593527</v>
+        <v>593481</v>
       </c>
       <c r="R11" t="n">
-        <v>6987563</v>
+        <v>6987561</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119916886</v>
+        <v>119917267</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593523</v>
+        <v>593527</v>
       </c>
       <c r="R12" t="n">
-        <v>6987471</v>
+        <v>6987563</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119916468</v>
+        <v>119916886</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593608</v>
+        <v>593523</v>
       </c>
       <c r="R13" t="n">
-        <v>6987529</v>
+        <v>6987471</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119916586</v>
+        <v>119916779</v>
       </c>
       <c r="B14" t="n">
-        <v>90084</v>
+        <v>77926</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1986,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>256703</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593618</v>
+        <v>593554</v>
       </c>
       <c r="R14" t="n">
-        <v>6987530</v>
+        <v>6987490</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119917551</v>
+        <v>119917111</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,25 +2088,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593594</v>
+        <v>593461</v>
       </c>
       <c r="R15" t="n">
-        <v>6987625</v>
+        <v>6987454</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
